--- a/backend/示例数据_测试导入.xlsx
+++ b/backend/示例数据_测试导入.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,10 +457,15 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>问题类型</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>整改期限</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>责任民警</t>
         </is>
@@ -482,32 +487,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>治安</t>
+          <t>行政</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>涉案财物问题</t>
+          <t>办案期限问题</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>调解协议书未上传</t>
+          <t>文书未开具</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>办案程序</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>刘警官</t>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>赵警官</t>
         </is>
       </c>
     </row>
@@ -527,7 +537,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -537,22 +547,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>初侦初查问题</t>
+          <t>涉案财物问题</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>调解协议书未上传,涉案物品未出入库</t>
+          <t>强制措施超期提醒,案件笔录未关联</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>笔录上传</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>张警官</t>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>赵警官</t>
         </is>
       </c>
     </row>
@@ -572,30 +587,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>刑事</t>
+          <t>治安</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>涉案财物问题</t>
+          <t>初侦初查问题</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>调解协议书未上传</t>
+          <t>文书未开具</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>音视频上传</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>王警官</t>
         </is>
@@ -617,12 +637,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>行政</t>
+          <t>刑事</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,12 +657,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>调查取证</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>李警官</t>
         </is>
       </c>
     </row>
@@ -662,12 +687,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>治安</t>
+          <t>刑事</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -677,17 +702,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>案件笔录未关联</t>
+          <t>强制措施超期提醒,调解协议书未上传,文书未开具</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>办案期限</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>李警官</t>
         </is>
       </c>
     </row>
@@ -707,32 +737,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>行政</t>
+          <t>刑事</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>办案期限问题</t>
+          <t>初侦初查问题</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>涉案物品未出入库,强制措施超期提醒,案件笔录未关联</t>
+          <t>未结案卷未归档</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>办案期限</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>李警官</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>张警官</t>
         </is>
       </c>
     </row>
@@ -752,32 +787,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>行政</t>
+          <t>治安</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>初侦初查问题</t>
+          <t>办案期限问题</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>调解协议书未上传</t>
+          <t>治安案件延长审批,调解协议书未上传,涉案物品未出入库</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>文书开具</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>王警官</t>
         </is>
       </c>
     </row>
@@ -797,32 +837,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>治安</t>
+          <t>刑事</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>初侦初查问题</t>
+          <t>涉案财物问题</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未结案卷未归档,执法音视频未上传,文书未开具</t>
+          <t>强制措施超期提醒,执法音视频未上传</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>调查取证</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>王警官</t>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>张警官</t>
         </is>
       </c>
     </row>
@@ -842,7 +887,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -852,22 +897,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>办案期限问题</t>
+          <t>涉案财物问题</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>强制措施超期提醒,文书未开具</t>
+          <t>强制措施超期提醒</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>办案期限</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>刘警官</t>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>陈警官</t>
         </is>
       </c>
     </row>
@@ -887,12 +937,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>治安</t>
+          <t>行政</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -902,17 +952,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>执法音视频未上传,文书未开具,强制措施超期提醒</t>
+          <t>案件笔录未关联,强制措施超期提醒</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>涉案财物</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>王警官</t>
         </is>
       </c>
     </row>
@@ -932,30 +987,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>行政</t>
+          <t>刑事</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>办案期限问题</t>
+          <t>初侦初查问题</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>文书未开具,强制措施超期提醒</t>
+          <t>案件笔录未关联</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>办案程序</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>赵警官</t>
         </is>
@@ -977,12 +1037,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>治安</t>
+          <t>刑事</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -992,17 +1052,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>调解协议书未上传,涉案物品未出入库,强制措施超期提醒</t>
+          <t>治安案件延长审批,案件笔录未关联,调解协议书未上传</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>涉案财物</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>李警官</t>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>王警官</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1087,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>刑事</t>
+          <t>治安</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>涉案财物问题</t>
+          <t>初侦初查问题</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>执法音视频未上传,文书未开具</t>
+          <t>治安案件延长审批,案件笔录未关联,文书未开具</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>办案程序</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>刘警官</t>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>陈警官</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1137,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>治安</t>
+          <t>行政</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1082,17 +1152,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>执法音视频未上传,案件笔录未关联,调解协议书未上传</t>
+          <t>调解协议书未上传,强制措施超期提醒,案件笔录未关联</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>音视频上传</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>王警官</t>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>赵警官</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1187,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>刑事</t>
+          <t>治安</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1127,17 +1202,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>调解协议书未上传,执法音视频未上传</t>
+          <t>强制措施超期提醒,未结案卷未归档</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>办案期限</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>刘警官</t>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>张警官</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1288,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>劳资纠纷</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>居民张某与李某因楼上漏水问题产生纠纷，双方情绪激动，需要及时调解处理。</t>
+          <t>小区业主因宠物饲养问题产生纠纷，需要社区介入协调。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1228,7 +1308,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>李警官</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1248,7 +1328,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>邻里矛盾</t>
+          <t>物业纠纷</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1258,7 +1338,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1268,7 +1348,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>李警官</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1288,32 +1368,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>邻里矛盾</t>
+          <t>物业纠纷</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>商铺租户与房东因租金上涨问题产生分歧，双方协商未果，需要调解介入。</t>
+          <t>物业公司与业主因物业费收取问题产生纠纷，需要协调处理。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>王警官</t>
+          <t>刘警官</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>待化解</t>
+          <t>待关注</t>
         </is>
       </c>
     </row>
@@ -1328,32 +1408,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>劳资纠纷</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>业主王某长期占用公共停车位，引发其他业主不满，物业协调未果。</t>
+          <t>家庭成员因财产分割问题产生争议，情绪激烈，需要调解。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>王警官</t>
+          <t>张警官</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>待化解</t>
+          <t>待关注</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1453,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>业主王某长期占用公共停车位，引发其他业主不满，物业协调未果。</t>
+          <t>家庭成员因财产分割问题产生争议，情绪激烈，需要调解。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1388,7 +1468,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>赵警官</t>
+          <t>王警官</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1408,17 +1488,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>邻里矛盾</t>
+          <t>家庭矛盾</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>家庭成员因财产分割问题产生争议，情绪激烈，需要调解。</t>
+          <t>商铺租户与房东因租金上涨问题产生分歧，双方协商未果，需要调解介入。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1428,12 +1508,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>王警官</t>
+          <t>赵警官</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>调解中</t>
+          <t>待关注</t>
         </is>
       </c>
     </row>
@@ -1448,32 +1528,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>物业纠纷</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>商铺租户与房东因租金上涨问题产生分歧，双方协商未果，需要调解介入。</t>
+          <t>物业公司与业主因物业费收取问题产生纠纷，需要协调处理。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>张警官</t>
+          <t>王警官</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>已调解</t>
+          <t>待化解</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1568,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>邻里矛盾</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>业主王某长期占用公共停车位，引发其他业主不满，物业协调未果。</t>
+          <t>员工与企业因工资发放问题产生劳资纠纷，申请调解。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1513,7 +1593,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>待化解</t>
+          <t>待关注</t>
         </is>
       </c>
     </row>
@@ -1528,22 +1608,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>物业纠纷</t>
+          <t>家庭矛盾</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>家庭成员因财产分割问题产生争议，情绪激烈，需要调解。</t>
+          <t>业主王某长期占用公共停车位，引发其他业主不满，物业协调未果。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1568,7 +1648,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>家庭矛盾</t>
+          <t>物业纠纷</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1578,17 +1658,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>赵警官</t>
+          <t>陈警官</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1608,17 +1688,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家庭矛盾</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>居民张某与李某因楼上漏水问题产生纠纷，双方情绪激动，需要及时调解处理。</t>
+          <t>小区业主因宠物饲养问题产生纠纷，需要社区介入协调。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1633,7 +1713,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>待关注</t>
+          <t>已调解</t>
         </is>
       </c>
     </row>
@@ -1648,17 +1728,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>邻里矛盾</t>
+          <t>物业纠纷</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>员工与企业因工资发放问题产生劳资纠纷，申请调解。</t>
+          <t>小区业主因宠物饲养问题产生纠纷，需要社区介入协调。</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1748,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>张警官</t>
+          <t>王警官</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>调解中</t>
+          <t>已调解</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1768,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>物业纠纷</t>
+          <t>劳资纠纷</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1698,7 +1778,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1708,7 +1788,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>赵警官</t>
+          <t>李警官</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1728,32 +1808,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>劳资纠纷</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>员工与企业因工资发放问题产生劳资纠纷，申请调解。</t>
+          <t>邻居因装修噪音问题产生矛盾，多次沟通无果，申请调解。</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>李警官</t>
+          <t>张警官</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>调解中</t>
+          <t>已调解</t>
         </is>
       </c>
     </row>
@@ -1768,32 +1848,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>劳资纠纷</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>业主王某长期占用公共停车位，引发其他业主不满，物业协调未果。</t>
+          <t>商铺租户与房东因租金上涨问题产生分歧，双方协商未果，需要调解介入。</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>李警官</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>待化解</t>
+          <t>待关注</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1898,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1828,7 +1908,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>赵警官</t>
+          <t>李警官</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1853,27 +1933,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>商铺租户与房东因租金上涨问题产生分歧，双方协商未果，需要调解介入。</t>
+          <t>家庭成员因财产分割问题产生争议，情绪激烈，需要调解。</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>刘警官</t>
+          <t>陈警官</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>已调解</t>
+          <t>调解中</t>
         </is>
       </c>
     </row>
@@ -1888,32 +1968,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>劳资纠纷</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>居民张某与李某因楼上漏水问题产生纠纷，双方情绪激动，需要及时调解处理。</t>
+          <t>员工与企业因工资发放问题产生劳资纠纷，申请调解。</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>陈警官</t>
+          <t>王警官</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>待化解</t>
+          <t>调解中</t>
         </is>
       </c>
     </row>
@@ -1933,17 +2013,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>物业公司与业主因物业费收取问题产生纠纷，需要协调处理。</t>
+          <t>居民张某与李某因楼上漏水问题产生纠纷，双方情绪激动，需要及时调解处理。</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1953,7 +2033,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>已调解</t>
+          <t>调解中</t>
         </is>
       </c>
     </row>
@@ -1973,27 +2053,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>邻居因装修噪音问题产生矛盾，多次沟通无果，申请调解。</t>
+          <t>物业公司与业主因物业费收取问题产生纠纷，需要协调处理。</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>赵警官</t>
+          <t>王警官</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>调解中</t>
+          <t>待化解</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,7 +2129,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2064,11 +2144,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>和平小区</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2077,26 +2157,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>新型侵财</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>抢夺</t>
+          <t>通讯网络诈骗</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2105,17 +2185,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>其它诈骗</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2124,7 +2204,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2133,7 +2213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2143,7 +2223,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>家庭暴力</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2152,7 +2232,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2161,26 +2241,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>其它诈骗</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>沈家门社区</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2189,26 +2269,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>沈家门街道</t>
+          <t>和平小区</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2217,26 +2297,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>普陀区西部</t>
+          <t>展茅街道</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2245,22 +2325,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>家庭暴力</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>普陀区西部</t>
+          <t>六横社区</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2278,21 +2358,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>新型侵财</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>通讯网络诈骗</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>六横社区</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2301,22 +2381,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>六横镇</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2329,22 +2409,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>新型侵财</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>通讯网络诈骗</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2357,7 +2437,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2372,11 +2452,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>普陀区南部</t>
+          <t>普陀区西部</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2385,22 +2465,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>普陀区南部</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2413,26 +2493,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>家庭暴力</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>普陀区南部</t>
+          <t>六横社区</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2441,7 +2521,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2451,16 +2531,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>抢夺</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>沈家门小区</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2469,22 +2549,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>其它诈骗</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>和平小区</t>
+          <t>东港小区</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2497,22 +2577,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>六横镇</t>
+          <t>桃花社区</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2530,21 +2610,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>沈家门社区</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2553,7 +2633,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2563,12 +2643,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>其它诈骗</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>沈家门小区</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2581,26 +2661,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>东港街道</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2609,26 +2689,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>桃花社区</t>
+          <t>普陀区东部</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2637,26 +2717,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>东港小区</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2665,7 +2745,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2675,16 +2755,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>抢夺</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>沈家门小区</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2693,26 +2773,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>沈家门社区</t>
+          <t>沈家门小区</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2721,22 +2801,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>展茅社区</t>
+          <t>展茅街道</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2749,22 +2829,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>其它诈骗</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>普陀区西部</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2777,26 +2857,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2805,7 +2885,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2820,11 +2900,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>展茅街道</t>
+          <t>东港街道</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2833,26 +2913,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>其它诈骗</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>普陀区南部</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2861,26 +2941,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>六横社区</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2889,22 +2969,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>展茅街道</t>
+          <t>东港小区</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2917,22 +2997,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>新型侵财</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>通讯网络诈骗</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>六横社区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2945,7 +3025,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2960,11 +3040,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2973,22 +3053,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>普陀区北部</t>
+          <t>沈家门街道</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -3001,7 +3081,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3011,16 +3091,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>和平小区</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -3029,26 +3109,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>展茅小区</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -3057,17 +3137,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3076,7 +3156,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3085,22 +3165,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>家庭暴力</t>
+          <t>其它诈骗</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>普陀区南部</t>
+          <t>东港小区</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -3113,22 +3193,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>和平小区</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -3141,26 +3221,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>展茅街道</t>
+          <t>普陀区西部</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -3169,17 +3249,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>新型侵财</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>通讯网络诈骗</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3197,22 +3277,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>六横社区</t>
+          <t>六横镇</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3225,26 +3305,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>东港街道</t>
+          <t>普陀区西部</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -3253,7 +3333,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3263,16 +3343,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>普陀区东部</t>
+          <t>普陀区南部</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3281,26 +3361,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>桃花社区</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3309,26 +3389,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>和平小区</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3337,26 +3417,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>和平小区</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3365,22 +3445,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>展茅小区</t>
+          <t>普陀区中部</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -3393,26 +3473,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>涉赌类</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>涉赌</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>六横镇</t>
+          <t>展茅社区</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3421,26 +3501,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>普陀区南部</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3449,22 +3529,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>沈家门社区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3477,26 +3557,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>普陀区东部</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3505,26 +3585,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>和平小区</t>
+          <t>东港社区</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3533,7 +3613,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3543,7 +3623,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>抢夺</t>
+          <t>其它诈骗</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3552,7 +3632,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3561,22 +3641,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>和平小区</t>
+          <t>沈家门街道</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3589,26 +3669,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>涉黄类</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>涉黄</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>普陀区南部</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3617,7 +3697,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3627,12 +3707,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>普陀区中部</t>
+          <t>普陀区西部</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -3645,7 +3725,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3655,7 +3735,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>抢夺</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3664,7 +3744,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3673,26 +3753,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>其它诈骗</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>普陀区中部</t>
+          <t>东港小区</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3701,22 +3781,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>抢夺</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>沈家门社区</t>
+          <t>沈家门小区</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -3729,26 +3809,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>打架斗殴</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>朱家尖小区</t>
+          <t>普陀区西部</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -3757,22 +3837,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>普陀区西部</t>
+          <t>六横社区</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3785,26 +3865,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>新型侵财</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>通讯网络诈骗</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>东港社区</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3813,26 +3893,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>偷盗类</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>沈家门街道</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -3841,7 +3921,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3851,16 +3931,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>其它诈骗</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>展茅小区</t>
+          <t>沈家门小区</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3869,7 +3949,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3879,7 +3959,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>抢夺</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3897,7 +3977,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3925,7 +4005,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3940,11 +4020,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>六横镇</t>
+          <t>东港街道</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3953,26 +4033,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>纠纷类</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>家庭暴力</t>
+          <t>纠纷</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>普陀区东部</t>
+          <t>沈家门社区</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3981,26 +4061,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>传统侵财</t>
+          <t>涉黄类</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>其它诈骗</t>
+          <t>涉黄</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>展茅小区</t>
+          <t>朱家尖小区</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4009,26 +4089,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>普陀区东部</t>
+          <t>沈家门街道</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4037,22 +4117,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>纠纷类</t>
+          <t>人身伤害</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>纠纷</t>
+          <t>家庭暴力</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>展茅社区</t>
+          <t>普陀区南部</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4065,22 +4145,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>新型侵财</t>
+          <t>传统侵财</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>通讯网络诈骗</t>
+          <t>偷盗类</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>沈家门小区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -4093,7 +4173,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4108,11 +4188,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>东港小区</t>
+          <t>展茅小区</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4121,138 +4201,26 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>人身伤害</t>
+          <t>涉赌类</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>打架斗殴</t>
+          <t>涉赌</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>普陀区北部</t>
+          <t>桃花镇</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>纠纷类</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>纠纷</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>六横社区</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>传统侵财</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>抢夺</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>和平小区</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>新型侵财</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>通讯网络诈骗</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>朱家尖小区</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>人身伤害</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>打架斗殴</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>普陀区北部</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4266,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4297,12 +4265,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -4315,16 +4283,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4333,16 +4301,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4351,16 +4319,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4369,16 +4337,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4387,16 +4355,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4405,16 +4373,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4423,16 +4391,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -4441,16 +4409,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4459,16 +4427,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -4477,12 +4445,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4495,16 +4463,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -4513,16 +4481,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -4531,12 +4499,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4549,16 +4517,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -4567,16 +4535,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -4585,16 +4553,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4603,16 +4571,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4621,12 +4589,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4639,12 +4607,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4657,16 +4625,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -4675,16 +4643,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4693,16 +4661,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4711,16 +4679,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4729,16 +4697,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4747,16 +4715,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4765,16 +4733,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4783,16 +4751,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -4801,16 +4769,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4819,16 +4787,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -4837,7 +4805,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4846,7 +4814,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -4855,7 +4823,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4864,7 +4832,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -4873,16 +4841,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -4891,16 +4859,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -4909,16 +4877,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -4927,16 +4895,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -4945,16 +4913,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -4963,16 +4931,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -4981,16 +4949,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -4999,16 +4967,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -5017,16 +4985,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -5035,12 +5003,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5053,7 +5021,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5062,7 +5030,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -5071,16 +5039,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -5089,16 +5057,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -5107,16 +5075,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -5125,16 +5093,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -5143,12 +5111,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5161,7 +5129,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5170,7 +5138,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -5179,16 +5147,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -5197,16 +5165,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -5215,7 +5183,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5233,16 +5201,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -5251,16 +5219,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -5269,12 +5237,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -5287,7 +5255,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5296,7 +5264,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -5305,16 +5273,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -5323,16 +5291,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -5341,16 +5309,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -5359,16 +5327,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -5377,16 +5345,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -5395,12 +5363,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -5413,16 +5381,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -5431,16 +5399,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -5449,16 +5417,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -5467,16 +5435,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -5485,16 +5453,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -5503,7 +5471,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5512,7 +5480,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -5521,16 +5489,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -5539,16 +5507,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -5557,16 +5525,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -5575,16 +5543,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -5593,7 +5561,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5602,7 +5570,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -5611,16 +5579,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -5629,7 +5597,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5638,7 +5606,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -5647,16 +5615,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -5665,16 +5633,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -5683,16 +5651,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -5701,12 +5669,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -5719,7 +5687,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5737,16 +5705,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -5755,16 +5723,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5773,16 +5741,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5791,7 +5759,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5809,16 +5777,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -5827,16 +5795,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -5845,16 +5813,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -5863,7 +5831,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5872,7 +5840,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5881,7 +5849,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5890,7 +5858,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -5899,16 +5867,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -5917,16 +5885,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -5935,16 +5903,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -5953,16 +5921,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -5971,16 +5939,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -5989,12 +5957,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -6007,16 +5975,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -6025,16 +5993,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -6043,16 +6011,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -6061,16 +6029,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -6079,12 +6047,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -6097,16 +6065,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -6115,16 +6083,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -6133,16 +6101,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -6151,16 +6119,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -6169,16 +6137,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -6187,16 +6155,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6205,16 +6173,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -6223,16 +6191,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -6241,7 +6209,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6259,7 +6227,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6277,7 +6245,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6286,7 +6254,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -6295,16 +6263,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
@@ -6313,12 +6281,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -6331,12 +6299,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -6349,16 +6317,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -6367,12 +6335,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -6385,12 +6353,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -6403,12 +6371,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -6421,16 +6389,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -6439,12 +6407,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -6457,16 +6425,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -6475,16 +6443,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -6493,16 +6461,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -6511,16 +6479,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -6529,16 +6497,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -6547,16 +6515,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -6565,16 +6533,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -6583,16 +6551,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
@@ -6601,12 +6569,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -6619,12 +6587,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -6637,16 +6605,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -6655,16 +6623,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -6673,16 +6641,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -6691,16 +6659,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -6709,16 +6677,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -6727,16 +6695,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -6745,16 +6713,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -6763,16 +6731,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -6781,7 +6749,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6790,7 +6758,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -6799,16 +6767,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
@@ -6817,7 +6785,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6826,7 +6794,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -6835,16 +6803,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -6853,16 +6821,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -6871,16 +6839,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146">
@@ -6889,16 +6857,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -6907,16 +6875,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -6925,16 +6893,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
@@ -6943,16 +6911,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -6961,16 +6929,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -6979,16 +6947,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -6997,12 +6965,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -7015,16 +6983,16 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -7033,7 +7001,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7042,7 +7010,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -7051,16 +7019,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
@@ -7069,7 +7037,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7078,7 +7046,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -7087,16 +7055,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
@@ -7105,16 +7073,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -7123,16 +7091,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
@@ -7141,16 +7109,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
@@ -7159,7 +7127,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7168,7 +7136,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
@@ -7177,16 +7145,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163">
@@ -7195,16 +7163,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -7213,16 +7181,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -7231,7 +7199,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7240,7 +7208,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -7249,16 +7217,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -7267,16 +7235,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -7285,16 +7253,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -7303,16 +7271,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
@@ -7321,16 +7289,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
@@ -7339,7 +7307,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7348,7 +7316,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
@@ -7357,12 +7325,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -7375,16 +7343,16 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -7393,16 +7361,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -7411,12 +7379,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -7429,16 +7397,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177">
@@ -7447,16 +7415,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -7465,16 +7433,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -7483,16 +7451,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
@@ -7501,16 +7469,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -7519,7 +7487,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7528,7 +7496,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182">
@@ -7537,12 +7505,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7555,16 +7523,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
@@ -7573,16 +7541,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -7591,16 +7559,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -7609,16 +7577,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
@@ -7627,16 +7595,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -7645,16 +7613,16 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -7668,11 +7636,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -7686,11 +7654,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -7699,7 +7667,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7708,7 +7676,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -7726,7 +7694,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -7740,7 +7708,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7753,7 +7721,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7771,16 +7739,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
@@ -7789,16 +7757,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -7812,11 +7780,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -7830,11 +7798,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
@@ -7843,16 +7811,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -7861,16 +7829,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -7884,11 +7852,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -7902,11 +7870,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -7915,16 +7883,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -7938,11 +7906,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -7956,7 +7924,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7974,11 +7942,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -7996,7 +7964,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
@@ -8010,11 +7978,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209">
@@ -8028,11 +7996,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210">
@@ -8041,16 +8009,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -8068,7 +8036,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -8082,11 +8050,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -8100,11 +8068,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -8118,11 +8086,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
@@ -8136,11 +8104,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -8154,11 +8122,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -8167,16 +8135,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -8185,16 +8153,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -8208,7 +8176,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8226,11 +8194,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -8244,11 +8212,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -8257,16 +8225,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223">
@@ -8275,16 +8243,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
@@ -8298,11 +8266,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225">
@@ -8316,11 +8284,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -8338,7 +8306,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -8347,16 +8315,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>沈家门街道和平路128号</t>
+          <t>东港小区3号楼</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228">
@@ -8370,11 +8338,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -8388,11 +8356,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>朱家尖小区4号楼</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -8406,7 +8374,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>东港小区5号楼</t>
+          <t>展茅小区6号楼</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8419,16 +8387,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>展茅小区6号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
@@ -8442,11 +8410,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>沈家门小区2号楼</t>
+          <t>沈家门街道和平路128号</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
@@ -8464,7 +8432,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234">
@@ -8478,7 +8446,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>和平小区1号楼</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -8491,16 +8459,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>东港小区门口</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -8518,7 +8486,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -8532,7 +8500,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>和平小区1号楼</t>
+          <t>东港小区5号楼</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -8550,11 +8518,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>朱家尖小区4号楼</t>
+          <t>沈家门小区2号楼</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -8563,213 +8531,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>东港小区3号楼</t>
+          <t>东港小区门口</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>239</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>朱家尖小区4号楼</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>240</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>沈家门小区2号楼</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>241</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>沈家门街道和平路128号</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>242</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>展茅小区6号楼</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>243</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>和平小区1号楼</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>244</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>沈家门小区2号楼</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>245</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>朱家尖小区4号楼</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>246</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>沈家门小区2号楼</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>247</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>展茅小区6号楼</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>248</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>和平小区1号楼</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>249</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>东港小区5号楼</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
         <v>2</v>
       </c>
     </row>
